--- a/artfynd/A 45015-2024 artfynd.xlsx
+++ b/artfynd/A 45015-2024 artfynd.xlsx
@@ -2402,10 +2402,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121094268</v>
+        <v>121094320</v>
       </c>
       <c r="B17" t="n">
-        <v>97025</v>
+        <v>98071</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2414,41 +2414,50 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Nils-Olsbodarna, Nils-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>484195</v>
+        <v>484230</v>
       </c>
       <c r="R17" t="n">
-        <v>7009828</v>
+        <v>7009848</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2477,7 +2486,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2487,7 +2496,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2514,10 +2523,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121094320</v>
+        <v>121094268</v>
       </c>
       <c r="B18" t="n">
-        <v>98071</v>
+        <v>97025</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2526,50 +2535,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Nils-Olsbodarna, Nils-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>484230</v>
+        <v>484195</v>
       </c>
       <c r="R18" t="n">
-        <v>7009848</v>
+        <v>7009828</v>
       </c>
       <c r="S18" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 45015-2024 artfynd.xlsx
+++ b/artfynd/A 45015-2024 artfynd.xlsx
@@ -1135,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121093352</v>
+        <v>121094296</v>
       </c>
       <c r="B6" t="n">
-        <v>78598</v>
+        <v>98081</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,41 +1147,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Nils-Olsbodarna, Nils-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>484196</v>
+        <v>484195</v>
       </c>
       <c r="R6" t="n">
-        <v>7009855</v>
+        <v>7009828</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1210,7 +1219,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1220,7 +1229,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,10 +1256,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121093561</v>
+        <v>121093320</v>
       </c>
       <c r="B7" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1280,20 +1289,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nils-Olsbodarna, Jmt</t>
+          <t>Nils-Olsbodarna, Nils-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>484252</v>
+        <v>484220</v>
       </c>
       <c r="R7" t="n">
-        <v>7009880</v>
+        <v>7009860</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1322,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1332,7 +1345,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,22 +1360,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Per Sonnvik</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Per Sonnvik</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121093888</v>
+        <v>121093362</v>
       </c>
       <c r="B8" t="n">
-        <v>97025</v>
+        <v>98081</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1371,41 +1384,45 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Nils-Olsbodarna, Nils-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>484175</v>
+        <v>484200</v>
       </c>
       <c r="R8" t="n">
-        <v>7009761</v>
+        <v>7009850</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1434,7 +1451,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1444,7 +1461,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,10 +1488,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121093351</v>
+        <v>121094241</v>
       </c>
       <c r="B9" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1504,20 +1521,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Nils-Olsbodarna, Jmt</t>
+          <t>Nils-Olsbodarna, Nils-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>484237</v>
+        <v>484175</v>
       </c>
       <c r="R9" t="n">
-        <v>7009832</v>
+        <v>7009761</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1546,7 +1567,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1556,12 +1577,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>20 +</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,22 +1592,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Per Sonnvik</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Per Sonnvik</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121094175</v>
+        <v>121094320</v>
       </c>
       <c r="B10" t="n">
-        <v>74705</v>
+        <v>98081</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1600,41 +1616,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Nils-Olsbodarna, Nils-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>484175</v>
+        <v>484230</v>
       </c>
       <c r="R10" t="n">
-        <v>7009761</v>
+        <v>7009848</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1663,7 +1688,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1673,7 +1698,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1700,10 +1725,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121094108</v>
+        <v>121093561</v>
       </c>
       <c r="B11" t="n">
-        <v>90122</v>
+        <v>98081</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1712,45 +1737,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4189</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nils-Olsbodarna, Nils-Olsbodarna, Jmt</t>
+          <t>Nils-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>484175</v>
+        <v>484252</v>
       </c>
       <c r="R11" t="n">
-        <v>7009761</v>
+        <v>7009880</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1779,7 +1800,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1789,7 +1810,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1804,22 +1825,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Per Sonnvik</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Per Sonnvik</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121093320</v>
+        <v>121093351</v>
       </c>
       <c r="B12" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1849,24 +1870,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Nils-Olsbodarna, Nils-Olsbodarna, Jmt</t>
+          <t>Nils-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>484220</v>
+        <v>484237</v>
       </c>
       <c r="R12" t="n">
-        <v>7009860</v>
+        <v>7009832</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1895,7 +1912,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1905,7 +1922,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>20 +</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,22 +1942,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Per Sonnvik</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Per Sonnvik</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121094241</v>
+        <v>121094108</v>
       </c>
       <c r="B13" t="n">
-        <v>98071</v>
+        <v>90132</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1944,30 +1966,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>4189</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1982,7 +2004,7 @@
         <v>7009761</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2011,7 +2033,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2021,7 +2043,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2048,10 +2070,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121094296</v>
+        <v>121094175</v>
       </c>
       <c r="B14" t="n">
-        <v>98071</v>
+        <v>74708</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2060,50 +2082,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Nils-Olsbodarna, Nils-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>484195</v>
+        <v>484175</v>
       </c>
       <c r="R14" t="n">
-        <v>7009828</v>
+        <v>7009761</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2132,7 +2145,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2142,7 +2155,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2169,10 +2182,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121093998</v>
+        <v>121093888</v>
       </c>
       <c r="B15" t="n">
-        <v>98071</v>
+        <v>97035</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2181,41 +2194,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Nils-Olsbodarna, Jmt</t>
+          <t>Nils-Olsbodarna, Nils-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>484160</v>
+        <v>484175</v>
       </c>
       <c r="R15" t="n">
-        <v>7009720</v>
+        <v>7009761</v>
       </c>
       <c r="S15" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2244,7 +2257,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2254,12 +2267,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>100+</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2274,22 +2282,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Per Sonnvik</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Per Sonnvik</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121093362</v>
+        <v>121093998</v>
       </c>
       <c r="B16" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2319,24 +2327,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Nils-Olsbodarna, Nils-Olsbodarna, Jmt</t>
+          <t>Nils-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>484200</v>
+        <v>484160</v>
       </c>
       <c r="R16" t="n">
-        <v>7009850</v>
+        <v>7009720</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2365,7 +2369,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2375,7 +2379,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>100+</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2390,22 +2399,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Per Sonnvik</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Per Sonnvik</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121094320</v>
+        <v>121093352</v>
       </c>
       <c r="B17" t="n">
-        <v>98071</v>
+        <v>78601</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2414,50 +2423,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Nils-Olsbodarna, Nils-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>484230</v>
+        <v>484196</v>
       </c>
       <c r="R17" t="n">
-        <v>7009848</v>
+        <v>7009855</v>
       </c>
       <c r="S17" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2526,7 +2526,7 @@
         <v>121094268</v>
       </c>
       <c r="B18" t="n">
-        <v>97025</v>
+        <v>97035</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 45015-2024 artfynd.xlsx
+++ b/artfynd/A 45015-2024 artfynd.xlsx
@@ -2182,10 +2182,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121093888</v>
+        <v>121093998</v>
       </c>
       <c r="B15" t="n">
-        <v>97035</v>
+        <v>98081</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2194,41 +2194,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Nils-Olsbodarna, Nils-Olsbodarna, Jmt</t>
+          <t>Nils-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>484175</v>
+        <v>484160</v>
       </c>
       <c r="R15" t="n">
-        <v>7009761</v>
+        <v>7009720</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2267,7 +2267,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>100+</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2282,22 +2287,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Per Sonnvik</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Per Sonnvik</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121093998</v>
+        <v>121093888</v>
       </c>
       <c r="B16" t="n">
-        <v>98081</v>
+        <v>97035</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2306,41 +2311,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Nils-Olsbodarna, Jmt</t>
+          <t>Nils-Olsbodarna, Nils-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>484160</v>
+        <v>484175</v>
       </c>
       <c r="R16" t="n">
-        <v>7009720</v>
+        <v>7009761</v>
       </c>
       <c r="S16" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2369,7 +2374,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2379,12 +2384,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>100+</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2399,22 +2399,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Per Sonnvik</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Per Sonnvik</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121093352</v>
+        <v>121094268</v>
       </c>
       <c r="B17" t="n">
-        <v>78601</v>
+        <v>97035</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2423,25 +2423,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2451,13 +2451,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>484196</v>
+        <v>484195</v>
       </c>
       <c r="R17" t="n">
-        <v>7009855</v>
+        <v>7009828</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2523,10 +2523,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121094268</v>
+        <v>121093352</v>
       </c>
       <c r="B18" t="n">
-        <v>97035</v>
+        <v>78601</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2535,25 +2535,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>484195</v>
+        <v>484196</v>
       </c>
       <c r="R18" t="n">
-        <v>7009828</v>
+        <v>7009855</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 45015-2024 artfynd.xlsx
+++ b/artfynd/A 45015-2024 artfynd.xlsx
@@ -2182,10 +2182,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121093998</v>
+        <v>121093888</v>
       </c>
       <c r="B15" t="n">
-        <v>98081</v>
+        <v>97035</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2194,41 +2194,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Nils-Olsbodarna, Jmt</t>
+          <t>Nils-Olsbodarna, Nils-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>484160</v>
+        <v>484175</v>
       </c>
       <c r="R15" t="n">
-        <v>7009720</v>
+        <v>7009761</v>
       </c>
       <c r="S15" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2267,12 +2267,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>100+</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2287,22 +2282,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Per Sonnvik</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Per Sonnvik</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121093888</v>
+        <v>121093998</v>
       </c>
       <c r="B16" t="n">
-        <v>97035</v>
+        <v>98081</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2311,41 +2306,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Nils-Olsbodarna, Nils-Olsbodarna, Jmt</t>
+          <t>Nils-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>484175</v>
+        <v>484160</v>
       </c>
       <c r="R16" t="n">
-        <v>7009761</v>
+        <v>7009720</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2374,7 +2369,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2384,7 +2379,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>100+</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2399,22 +2399,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Per Sonnvik</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Per Sonnvik</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121094268</v>
+        <v>121093352</v>
       </c>
       <c r="B17" t="n">
-        <v>97035</v>
+        <v>78601</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2423,25 +2423,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2451,13 +2451,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>484195</v>
+        <v>484196</v>
       </c>
       <c r="R17" t="n">
-        <v>7009828</v>
+        <v>7009855</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2523,10 +2523,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121093352</v>
+        <v>121094268</v>
       </c>
       <c r="B18" t="n">
-        <v>78601</v>
+        <v>97035</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2535,25 +2535,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>484196</v>
+        <v>484195</v>
       </c>
       <c r="R18" t="n">
-        <v>7009855</v>
+        <v>7009828</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 45015-2024 artfynd.xlsx
+++ b/artfynd/A 45015-2024 artfynd.xlsx
@@ -1135,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121094296</v>
+        <v>121094108</v>
       </c>
       <c r="B6" t="n">
-        <v>98081</v>
+        <v>90132</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,35 +1147,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>4189</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1184,13 +1179,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>484195</v>
+        <v>484175</v>
       </c>
       <c r="R6" t="n">
-        <v>7009828</v>
+        <v>7009761</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1219,7 +1214,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1229,7 +1224,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,10 +1251,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121093320</v>
+        <v>121094175</v>
       </c>
       <c r="B7" t="n">
-        <v>98081</v>
+        <v>74708</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1268,45 +1263,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Nils-Olsbodarna, Nils-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>484220</v>
+        <v>484175</v>
       </c>
       <c r="R7" t="n">
-        <v>7009860</v>
+        <v>7009761</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1335,7 +1326,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,7 +1336,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,10 +1363,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121093362</v>
+        <v>121094268</v>
       </c>
       <c r="B8" t="n">
-        <v>98081</v>
+        <v>97035</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1384,45 +1375,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Nils-Olsbodarna, Nils-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>484200</v>
+        <v>484195</v>
       </c>
       <c r="R8" t="n">
-        <v>7009850</v>
+        <v>7009828</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1451,7 +1438,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1461,7 +1448,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,10 +1475,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121094241</v>
+        <v>121093888</v>
       </c>
       <c r="B9" t="n">
-        <v>98081</v>
+        <v>97035</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1500,32 +1487,28 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Nils-Olsbodarna, Nils-Olsbodarna, Jmt</t>
@@ -1538,7 +1521,7 @@
         <v>7009761</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1567,7 +1550,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1577,7 +1560,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1604,7 +1587,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121094320</v>
+        <v>121093320</v>
       </c>
       <c r="B10" t="n">
         <v>98081</v>
@@ -1639,12 +1622,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1653,13 +1631,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>484230</v>
+        <v>484220</v>
       </c>
       <c r="R10" t="n">
-        <v>7009848</v>
+        <v>7009860</v>
       </c>
       <c r="S10" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1688,7 +1666,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1698,7 +1676,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1725,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121093561</v>
+        <v>121093352</v>
       </c>
       <c r="B11" t="n">
-        <v>98081</v>
+        <v>78601</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1737,41 +1715,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nils-Olsbodarna, Jmt</t>
+          <t>Nils-Olsbodarna, Nils-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>484252</v>
+        <v>484196</v>
       </c>
       <c r="R11" t="n">
-        <v>7009880</v>
+        <v>7009855</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1800,7 +1778,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1810,7 +1788,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,19 +1803,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Per Sonnvik</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Per Sonnvik</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121093351</v>
+        <v>121093362</v>
       </c>
       <c r="B12" t="n">
         <v>98081</v>
@@ -1870,20 +1848,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Nils-Olsbodarna, Jmt</t>
+          <t>Nils-Olsbodarna, Nils-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>484237</v>
+        <v>484200</v>
       </c>
       <c r="R12" t="n">
-        <v>7009832</v>
+        <v>7009850</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1912,7 +1894,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1922,12 +1904,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>20 +</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1942,22 +1919,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Per Sonnvik</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Per Sonnvik</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121094108</v>
+        <v>121093998</v>
       </c>
       <c r="B13" t="n">
-        <v>90132</v>
+        <v>98081</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1966,45 +1943,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4189</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Nils-Olsbodarna, Nils-Olsbodarna, Jmt</t>
+          <t>Nils-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>484175</v>
+        <v>484160</v>
       </c>
       <c r="R13" t="n">
-        <v>7009761</v>
+        <v>7009720</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2033,7 +2006,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2043,7 +2016,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>100+</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2058,22 +2036,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Per Sonnvik</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Per Sonnvik</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121094175</v>
+        <v>121094320</v>
       </c>
       <c r="B14" t="n">
-        <v>74708</v>
+        <v>98081</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2082,41 +2060,50 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Nils-Olsbodarna, Nils-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>484175</v>
+        <v>484230</v>
       </c>
       <c r="R14" t="n">
-        <v>7009761</v>
+        <v>7009848</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2145,7 +2132,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2155,7 +2142,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2182,10 +2169,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121093888</v>
+        <v>121094296</v>
       </c>
       <c r="B15" t="n">
-        <v>97035</v>
+        <v>98081</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2194,41 +2181,50 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Nils-Olsbodarna, Nils-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>484175</v>
+        <v>484195</v>
       </c>
       <c r="R15" t="n">
-        <v>7009761</v>
+        <v>7009828</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2257,7 +2253,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2267,7 +2263,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2294,7 +2290,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121093998</v>
+        <v>121093351</v>
       </c>
       <c r="B16" t="n">
         <v>98081</v>
@@ -2334,13 +2330,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>484160</v>
+        <v>484237</v>
       </c>
       <c r="R16" t="n">
-        <v>7009720</v>
+        <v>7009832</v>
       </c>
       <c r="S16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2369,7 +2365,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2379,12 +2375,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>100+</t>
+          <t>20 +</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2411,10 +2407,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121093352</v>
+        <v>121094241</v>
       </c>
       <c r="B17" t="n">
-        <v>78601</v>
+        <v>98081</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2423,41 +2419,45 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Nils-Olsbodarna, Nils-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>484196</v>
+        <v>484175</v>
       </c>
       <c r="R17" t="n">
-        <v>7009855</v>
+        <v>7009761</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2523,10 +2523,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121094268</v>
+        <v>121093561</v>
       </c>
       <c r="B18" t="n">
-        <v>97035</v>
+        <v>98081</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2535,41 +2535,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nils-Olsbodarna, Nils-Olsbodarna, Jmt</t>
+          <t>Nils-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>484195</v>
+        <v>484252</v>
       </c>
       <c r="R18" t="n">
-        <v>7009828</v>
+        <v>7009880</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2623,12 +2623,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Per Sonnvik</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Per Sonnvik</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 45015-2024 artfynd.xlsx
+++ b/artfynd/A 45015-2024 artfynd.xlsx
@@ -1135,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121094108</v>
+        <v>121093351</v>
       </c>
       <c r="B6" t="n">
-        <v>90132</v>
+        <v>98094</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,45 +1147,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4189</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nils-Olsbodarna, Nils-Olsbodarna, Jmt</t>
+          <t>Nils-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>484175</v>
+        <v>484237</v>
       </c>
       <c r="R6" t="n">
-        <v>7009761</v>
+        <v>7009832</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1214,7 +1210,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1224,7 +1220,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>20 +</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,22 +1240,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Per Sonnvik</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Per Sonnvik</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121094175</v>
+        <v>121093320</v>
       </c>
       <c r="B7" t="n">
-        <v>74708</v>
+        <v>98094</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1263,41 +1264,45 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Nils-Olsbodarna, Nils-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>484175</v>
+        <v>484220</v>
       </c>
       <c r="R7" t="n">
-        <v>7009761</v>
+        <v>7009860</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1326,7 +1331,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1336,7 +1341,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,10 +1368,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121094268</v>
+        <v>121093362</v>
       </c>
       <c r="B8" t="n">
-        <v>97035</v>
+        <v>98094</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1375,41 +1380,45 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Nils-Olsbodarna, Nils-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>484195</v>
+        <v>484200</v>
       </c>
       <c r="R8" t="n">
-        <v>7009828</v>
+        <v>7009850</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1438,7 +1447,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1448,7 +1457,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1475,10 +1484,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121093888</v>
+        <v>121094296</v>
       </c>
       <c r="B9" t="n">
-        <v>97035</v>
+        <v>98094</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1487,41 +1496,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Nils-Olsbodarna, Nils-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>484175</v>
+        <v>484195</v>
       </c>
       <c r="R9" t="n">
-        <v>7009761</v>
+        <v>7009828</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1550,7 +1568,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1560,7 +1578,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,10 +1605,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121093320</v>
+        <v>121094108</v>
       </c>
       <c r="B10" t="n">
-        <v>98081</v>
+        <v>90140</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1599,30 +1617,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>4189</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1631,13 +1649,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>484220</v>
+        <v>484175</v>
       </c>
       <c r="R10" t="n">
-        <v>7009860</v>
+        <v>7009761</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1666,7 +1684,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1676,7 +1694,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,10 +1721,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121093352</v>
+        <v>121093888</v>
       </c>
       <c r="B11" t="n">
-        <v>78601</v>
+        <v>97048</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1715,25 +1733,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1743,13 +1761,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>484196</v>
+        <v>484175</v>
       </c>
       <c r="R11" t="n">
-        <v>7009855</v>
+        <v>7009761</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1778,7 +1796,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,7 +1806,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,10 +1833,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121093362</v>
+        <v>121093561</v>
       </c>
       <c r="B12" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1848,24 +1866,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Nils-Olsbodarna, Nils-Olsbodarna, Jmt</t>
+          <t>Nils-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>484200</v>
+        <v>484252</v>
       </c>
       <c r="R12" t="n">
-        <v>7009850</v>
+        <v>7009880</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1894,7 +1908,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1904,7 +1918,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1919,12 +1933,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Per Sonnvik</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Per Sonnvik</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1934,7 +1948,7 @@
         <v>121093998</v>
       </c>
       <c r="B13" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2048,10 +2062,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121094320</v>
+        <v>121093352</v>
       </c>
       <c r="B14" t="n">
-        <v>98081</v>
+        <v>78604</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2060,50 +2074,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Nils-Olsbodarna, Nils-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>484230</v>
+        <v>484196</v>
       </c>
       <c r="R14" t="n">
-        <v>7009848</v>
+        <v>7009855</v>
       </c>
       <c r="S14" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2132,7 +2137,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2142,7 +2147,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2169,10 +2174,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121094296</v>
+        <v>121094320</v>
       </c>
       <c r="B15" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2204,12 +2209,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2218,13 +2223,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>484195</v>
+        <v>484230</v>
       </c>
       <c r="R15" t="n">
-        <v>7009828</v>
+        <v>7009848</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2253,7 +2258,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2263,7 +2268,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2290,10 +2295,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121093351</v>
+        <v>121094175</v>
       </c>
       <c r="B16" t="n">
-        <v>98081</v>
+        <v>74710</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2302,41 +2307,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Nils-Olsbodarna, Jmt</t>
+          <t>Nils-Olsbodarna, Nils-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>484237</v>
+        <v>484175</v>
       </c>
       <c r="R16" t="n">
-        <v>7009832</v>
+        <v>7009761</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2365,7 +2370,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2375,12 +2380,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>20 +</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2395,12 +2395,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Per Sonnvik</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Per Sonnvik</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2410,7 +2410,7 @@
         <v>121094241</v>
       </c>
       <c r="B17" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2523,10 +2523,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121093561</v>
+        <v>121094268</v>
       </c>
       <c r="B18" t="n">
-        <v>98081</v>
+        <v>97048</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2535,41 +2535,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nils-Olsbodarna, Jmt</t>
+          <t>Nils-Olsbodarna, Nils-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>484252</v>
+        <v>484195</v>
       </c>
       <c r="R18" t="n">
-        <v>7009880</v>
+        <v>7009828</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2623,12 +2623,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Per Sonnvik</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Per Sonnvik</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 45015-2024 artfynd.xlsx
+++ b/artfynd/A 45015-2024 artfynd.xlsx
@@ -1135,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121093351</v>
+        <v>121093561</v>
       </c>
       <c r="B6" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>484237</v>
+        <v>484252</v>
       </c>
       <c r="R6" t="n">
-        <v>7009832</v>
+        <v>7009880</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1220,12 +1220,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>20 +</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,10 +1247,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121093320</v>
+        <v>121094320</v>
       </c>
       <c r="B7" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1287,7 +1282,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1296,13 +1296,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>484220</v>
+        <v>484230</v>
       </c>
       <c r="R7" t="n">
-        <v>7009860</v>
+        <v>7009848</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1368,10 +1368,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121093362</v>
+        <v>121093352</v>
       </c>
       <c r="B8" t="n">
-        <v>98094</v>
+        <v>78604</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1380,45 +1380,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Nils-Olsbodarna, Nils-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>484200</v>
+        <v>484196</v>
       </c>
       <c r="R8" t="n">
-        <v>7009850</v>
+        <v>7009855</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1447,7 +1443,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1457,7 +1453,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,10 +1480,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121094296</v>
+        <v>121094108</v>
       </c>
       <c r="B9" t="n">
-        <v>98094</v>
+        <v>90141</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1496,35 +1492,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>4189</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1533,13 +1524,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>484195</v>
+        <v>484175</v>
       </c>
       <c r="R9" t="n">
-        <v>7009828</v>
+        <v>7009761</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1568,7 +1559,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1578,7 +1569,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1605,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121094108</v>
+        <v>121093362</v>
       </c>
       <c r="B10" t="n">
-        <v>90140</v>
+        <v>98095</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1617,25 +1608,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4189</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1649,13 +1640,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>484175</v>
+        <v>484200</v>
       </c>
       <c r="R10" t="n">
-        <v>7009761</v>
+        <v>7009850</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1684,7 +1675,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1694,7 +1685,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1721,10 +1712,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121093888</v>
+        <v>121093998</v>
       </c>
       <c r="B11" t="n">
-        <v>97048</v>
+        <v>98095</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1733,41 +1724,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nils-Olsbodarna, Nils-Olsbodarna, Jmt</t>
+          <t>Nils-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>484175</v>
+        <v>484160</v>
       </c>
       <c r="R11" t="n">
-        <v>7009761</v>
+        <v>7009720</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1796,7 +1787,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1806,7 +1797,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>100+</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1821,22 +1817,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Per Sonnvik</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Per Sonnvik</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121093561</v>
+        <v>121093351</v>
       </c>
       <c r="B12" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1873,10 +1869,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>484252</v>
+        <v>484237</v>
       </c>
       <c r="R12" t="n">
-        <v>7009880</v>
+        <v>7009832</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1908,7 +1904,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1918,7 +1914,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>20 +</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1945,10 +1946,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121093998</v>
+        <v>121093320</v>
       </c>
       <c r="B13" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1978,20 +1979,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Nils-Olsbodarna, Jmt</t>
+          <t>Nils-Olsbodarna, Nils-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>484160</v>
+        <v>484220</v>
       </c>
       <c r="R13" t="n">
-        <v>7009720</v>
+        <v>7009860</v>
       </c>
       <c r="S13" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2020,7 +2025,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2030,12 +2035,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>100+</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2050,22 +2050,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Per Sonnvik</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Per Sonnvik</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121093352</v>
+        <v>121094241</v>
       </c>
       <c r="B14" t="n">
-        <v>78604</v>
+        <v>98095</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2074,41 +2074,45 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Nils-Olsbodarna, Nils-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>484196</v>
+        <v>484175</v>
       </c>
       <c r="R14" t="n">
-        <v>7009855</v>
+        <v>7009761</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2137,7 +2141,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2147,7 +2151,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2174,10 +2178,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121094320</v>
+        <v>121093888</v>
       </c>
       <c r="B15" t="n">
-        <v>98094</v>
+        <v>97049</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2186,50 +2190,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Nils-Olsbodarna, Nils-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>484230</v>
+        <v>484175</v>
       </c>
       <c r="R15" t="n">
-        <v>7009848</v>
+        <v>7009761</v>
       </c>
       <c r="S15" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2258,7 +2253,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2268,7 +2263,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2407,10 +2402,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121094241</v>
+        <v>121094268</v>
       </c>
       <c r="B17" t="n">
-        <v>98094</v>
+        <v>97049</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2419,45 +2414,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Nils-Olsbodarna, Nils-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>484175</v>
+        <v>484195</v>
       </c>
       <c r="R17" t="n">
-        <v>7009761</v>
+        <v>7009828</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2486,7 +2477,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2496,7 +2487,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2523,10 +2514,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121094268</v>
+        <v>121094296</v>
       </c>
       <c r="B18" t="n">
-        <v>97048</v>
+        <v>98095</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2535,28 +2526,37 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Nils-Olsbodarna, Nils-Olsbodarna, Jmt</t>
@@ -2569,7 +2569,7 @@
         <v>7009828</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 45015-2024 artfynd.xlsx
+++ b/artfynd/A 45015-2024 artfynd.xlsx
@@ -1135,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121093561</v>
+        <v>121093998</v>
       </c>
       <c r="B6" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,13 +1175,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>484252</v>
+        <v>484160</v>
       </c>
       <c r="R6" t="n">
-        <v>7009880</v>
+        <v>7009720</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1220,7 +1220,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>100+</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,10 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121094320</v>
+        <v>121093362</v>
       </c>
       <c r="B7" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,12 +1287,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1296,13 +1296,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>484230</v>
+        <v>484200</v>
       </c>
       <c r="R7" t="n">
-        <v>7009848</v>
+        <v>7009850</v>
       </c>
       <c r="S7" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1368,10 +1368,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121093352</v>
+        <v>121093320</v>
       </c>
       <c r="B8" t="n">
-        <v>78604</v>
+        <v>98098</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1380,41 +1380,45 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Nils-Olsbodarna, Nils-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>484196</v>
+        <v>484220</v>
       </c>
       <c r="R8" t="n">
-        <v>7009855</v>
+        <v>7009860</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1480,10 +1484,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121094108</v>
+        <v>121093561</v>
       </c>
       <c r="B9" t="n">
-        <v>90141</v>
+        <v>98098</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1492,45 +1496,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4189</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Nils-Olsbodarna, Nils-Olsbodarna, Jmt</t>
+          <t>Nils-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>484175</v>
+        <v>484252</v>
       </c>
       <c r="R9" t="n">
-        <v>7009761</v>
+        <v>7009880</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,22 +1584,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Per Sonnvik</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Per Sonnvik</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121093362</v>
+        <v>121094320</v>
       </c>
       <c r="B10" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1631,7 +1631,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1640,13 +1645,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>484200</v>
+        <v>484230</v>
       </c>
       <c r="R10" t="n">
-        <v>7009850</v>
+        <v>7009848</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1675,7 +1680,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1685,7 +1690,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1712,10 +1717,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121093998</v>
+        <v>121093888</v>
       </c>
       <c r="B11" t="n">
-        <v>98095</v>
+        <v>97052</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1724,41 +1729,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nils-Olsbodarna, Jmt</t>
+          <t>Nils-Olsbodarna, Nils-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>484160</v>
+        <v>484175</v>
       </c>
       <c r="R11" t="n">
-        <v>7009720</v>
+        <v>7009761</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1787,7 +1792,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1797,12 +1802,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>100+</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1817,22 +1817,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Per Sonnvik</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Per Sonnvik</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121093351</v>
+        <v>121094108</v>
       </c>
       <c r="B12" t="n">
-        <v>98095</v>
+        <v>90144</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1841,41 +1841,45 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>4189</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Nils-Olsbodarna, Jmt</t>
+          <t>Nils-Olsbodarna, Nils-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>484237</v>
+        <v>484175</v>
       </c>
       <c r="R12" t="n">
-        <v>7009832</v>
+        <v>7009761</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1904,7 +1908,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1914,12 +1918,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>20 +</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1934,22 +1933,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Per Sonnvik</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Per Sonnvik</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121093320</v>
+        <v>121093352</v>
       </c>
       <c r="B13" t="n">
-        <v>98095</v>
+        <v>78607</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1958,45 +1957,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Nils-Olsbodarna, Nils-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>484220</v>
+        <v>484196</v>
       </c>
       <c r="R13" t="n">
-        <v>7009860</v>
+        <v>7009855</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2062,10 +2057,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121094241</v>
+        <v>121094268</v>
       </c>
       <c r="B14" t="n">
-        <v>98095</v>
+        <v>97052</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2074,45 +2069,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Nils-Olsbodarna, Nils-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>484175</v>
+        <v>484195</v>
       </c>
       <c r="R14" t="n">
-        <v>7009761</v>
+        <v>7009828</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2141,7 +2132,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2151,7 +2142,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2178,10 +2169,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121093888</v>
+        <v>121094241</v>
       </c>
       <c r="B15" t="n">
-        <v>97049</v>
+        <v>98098</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2190,28 +2181,32 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Nils-Olsbodarna, Nils-Olsbodarna, Jmt</t>
@@ -2224,7 +2219,7 @@
         <v>7009761</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2253,7 +2248,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2263,7 +2258,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2293,7 +2288,7 @@
         <v>121094175</v>
       </c>
       <c r="B16" t="n">
-        <v>74710</v>
+        <v>74713</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2402,10 +2397,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121094268</v>
+        <v>121094296</v>
       </c>
       <c r="B17" t="n">
-        <v>97049</v>
+        <v>98098</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2414,28 +2409,37 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Nils-Olsbodarna, Nils-Olsbodarna, Jmt</t>
@@ -2448,7 +2452,7 @@
         <v>7009828</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2477,7 +2481,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2487,7 +2491,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2514,10 +2518,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121094296</v>
+        <v>121093351</v>
       </c>
       <c r="B18" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2547,29 +2551,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nils-Olsbodarna, Nils-Olsbodarna, Jmt</t>
+          <t>Nils-Olsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>484195</v>
+        <v>484237</v>
       </c>
       <c r="R18" t="n">
-        <v>7009828</v>
+        <v>7009832</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2598,7 +2593,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2608,7 +2603,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>20 +</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2623,12 +2623,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Per Sonnvik</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Per Sonnvik</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
